--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9C68F2-7412-4464-BE5E-1CCB567C06FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DED6E8-68A5-4DE8-BFF9-2012B24080C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1188,8 +1188,8 @@
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
@@ -1207,7 +1207,7 @@
     <col min="31" max="32" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.21875" customWidth="1"/>
-    <col min="35" max="35" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="71" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="46.33203125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -4606,8 +4606,9 @@
   <dimension ref="A1:BA19"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="34" max="34" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="23.33203125" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="21.109375" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="7.77734375" customWidth="1"/>
     <col min="37" max="37" width="38.88671875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="8.33203125" customWidth="1"/>

--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DED6E8-68A5-4DE8-BFF9-2012B24080C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D4380C-F223-47E9-A718-3BDCEE6D91FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="244">
   <si>
     <t>2026-2027 賽季 新北中信特攻 (TPBL) 例行賽球員攻守數據表 - 平均數據 (待賽程展開)</t>
   </si>
@@ -675,31 +675,85 @@
     <t>法拉帝 + 強斯</t>
   </si>
   <si>
-    <t>內外兼修(兩分50% / 三分50%)，多點分布</t>
-  </si>
-  <si>
-    <t>首秀狂抓15籃板攻下19分繳出大號雙十，內線終結效率高，特攻禁區攻守中樞。</t>
-  </si>
-  <si>
-    <t>外線投射為主(三分佔比89%)，空檔把握</t>
-  </si>
-  <si>
-    <t>飆進3記三分挹注11分3籃板3助攻並送出4次抄截，外圍第一線防守侵略性強。</t>
-  </si>
-  <si>
-    <t>轉換快攻與切入終結(兩分佔比62%)</t>
-  </si>
-  <si>
-    <t>先發出戰34分鐘拿下14分4抄截4助攻，首節推進帶動一波流，下半場遭嚴密包夾。</t>
-  </si>
-  <si>
-    <t>外線冷箭與陣地指揮(三分佔比83%)</t>
-  </si>
-  <si>
-    <t>傷癒復出替補17分鐘三分球5投3中高效率得9分4籃板，外線手感維持水準。</t>
-  </si>
-  <si>
-    <t>N/A</t>
+    <t>面框強攻與外線投射(外圍出手佔比43%)</t>
+  </si>
+  <si>
+    <t>首戰外線手感低迷繳6分6板3阻攻，具備高機動性與護框能力，待找回投籃手感。</t>
+  </si>
+  <si>
+    <t>外線定點投射(三分佔比89%)</t>
+  </si>
+  <si>
+    <t>首秀飆進3記三分挹注11分4抄截3助攻，特攻外圍第一射手兼第一線外線大鎖。</t>
+  </si>
+  <si>
+    <t>禁區護框洋將(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>待例行賽賽程展開 / 先列入註冊名單與數據架構。</t>
+  </si>
+  <si>
+    <t>禁區護框與卡位衝搶(前場籃板意識強)</t>
+  </si>
+  <si>
+    <t>首戰抓下9籃板(含4前場板)得5分，提供扎實內線卡位與籃板屏障。</t>
+  </si>
+  <si>
+    <t>內外兼修(兩分50% / 三分50%)，多點分佈</t>
+  </si>
+  <si>
+    <t>首秀狂砍19分15籃板(5前板)大號雙十，內線終結極高效率，特攻攻守真核。</t>
+  </si>
+  <si>
+    <t>轉換快攻與切入突破(衝擊籃框為主)</t>
+  </si>
+  <si>
+    <t>首戰貢獻14分4抄截4助攻，閃電快攻箭頭，具備頂級快攻推進與抄截威脅。</t>
+  </si>
+  <si>
+    <t>外線冷箭與突分(三分命中率50%)</t>
+  </si>
+  <si>
+    <t>替補19分鐘命中2記三分得6分2籃板，二陣外圍具備隨插即用的得分爆發力。</t>
+  </si>
+  <si>
+    <t>擋拆推進與全場導傳(助攻失誤比3.0)</t>
+  </si>
+  <si>
+    <t>先發主控繳出7分6助攻5籃板3抄截，流暢掌控快節奏推進與外圍導傳。</t>
+  </si>
+  <si>
+    <t>外線定點射手(外圍拉開空間)</t>
+  </si>
+  <si>
+    <t>替補出戰8分鐘出手2記三分未果，球隊純射手輪替，負責側翼空間牽制。</t>
+  </si>
+  <si>
+    <t>側翼防守射手(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>高位策應與禁區軸心(傳球視野開闊)</t>
+  </si>
+  <si>
+    <t>出賽近2分鐘主要提供高位戰術策應與防守掩護，老將經驗穩定軍心。</t>
+  </si>
+  <si>
+    <t>空手走位與快攻終結(兩分佔比100%)</t>
+  </si>
+  <si>
+    <t>替補8分鐘兩分4中2得4分2籃板，跑動積極，提供側翼扎實空切活力。</t>
+  </si>
+  <si>
+    <t>外線砲塔射手(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>替補控衛組織(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>陣地戰指揮官與外線跳投(三分命中率60%)</t>
+  </si>
+  <si>
+    <t>傷癒復出替補18分鐘三分5中3高效率拿9分4籃板，外圍準星依舊犀利。</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1260,7 @@
     <col min="30" max="30" width="3.77734375" bestFit="1" customWidth="1"/>
     <col min="31" max="32" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.21875" customWidth="1"/>
+    <col min="34" max="34" width="36.5546875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="71" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="46.33203125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="13.88671875" bestFit="1" customWidth="1"/>
@@ -1652,11 +1706,11 @@
       <c r="AG5" s="8">
         <v>1</v>
       </c>
-      <c r="AH5" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI5" s="6" t="s">
-        <v>225</v>
+      <c r="AH5" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI5" s="26" t="s">
+        <v>218</v>
       </c>
       <c r="AK5" s="24" t="s">
         <v>187</v>
@@ -1821,7 +1875,7 @@
       <c r="AG6" s="8">
         <v>3</v>
       </c>
-      <c r="AH6" s="28" t="s">
+      <c r="AH6" s="27" t="s">
         <v>219</v>
       </c>
       <c r="AI6" s="29" t="s">
@@ -1990,11 +2044,11 @@
       <c r="AG7" s="8">
         <v>0</v>
       </c>
-      <c r="AH7" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI7" s="6" t="s">
-        <v>225</v>
+      <c r="AH7" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="AI7" s="26" t="s">
+        <v>222</v>
       </c>
       <c r="AK7" s="24" t="s">
         <v>189</v>
@@ -2159,11 +2213,11 @@
       <c r="AG8" s="8">
         <v>0.5</v>
       </c>
-      <c r="AH8" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI8" s="6" t="s">
-        <v>225</v>
+      <c r="AH8" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="AI8" s="29" t="s">
+        <v>224</v>
       </c>
       <c r="AK8" s="27" t="s">
         <v>114</v>
@@ -2302,11 +2356,11 @@
       <c r="AG9" s="8">
         <v>0</v>
       </c>
-      <c r="AH9" s="25" t="s">
-        <v>217</v>
+      <c r="AH9" s="24" t="s">
+        <v>225</v>
       </c>
       <c r="AI9" s="26" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AK9" s="24" t="s">
         <v>190</v>
@@ -2445,11 +2499,11 @@
       <c r="AG10" s="8">
         <v>2</v>
       </c>
-      <c r="AH10" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI10" s="26" t="s">
-        <v>222</v>
+      <c r="AH10" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="AI10" s="29" t="s">
+        <v>228</v>
       </c>
       <c r="AK10" s="27" t="s">
         <v>191</v>
@@ -2588,11 +2642,11 @@
       <c r="AG11" s="8">
         <v>0</v>
       </c>
-      <c r="AH11" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI11" s="6" t="s">
-        <v>225</v>
+      <c r="AH11" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI11" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="AK11" s="24" t="s">
         <v>192</v>
@@ -2731,11 +2785,11 @@
       <c r="AG12" s="8">
         <v>3</v>
       </c>
-      <c r="AH12" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI12" s="6" t="s">
-        <v>225</v>
+      <c r="AH12" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="AI12" s="29" t="s">
+        <v>232</v>
       </c>
       <c r="AK12" s="27" t="s">
         <v>193</v>
@@ -2874,11 +2928,11 @@
       <c r="AG13" s="8">
         <v>0</v>
       </c>
-      <c r="AH13" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI13" s="6" t="s">
-        <v>225</v>
+      <c r="AH13" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="AI13" s="26" t="s">
+        <v>234</v>
       </c>
       <c r="AK13" s="24" t="s">
         <v>194</v>
@@ -3017,11 +3071,11 @@
       <c r="AG14" s="8">
         <v>0</v>
       </c>
-      <c r="AH14" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI14" s="6" t="s">
-        <v>225</v>
+      <c r="AH14" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="AI14" s="29" t="s">
+        <v>222</v>
       </c>
       <c r="AK14" s="17"/>
       <c r="AL14" s="17"/>
@@ -3146,11 +3200,11 @@
       <c r="AG15" s="8">
         <v>0</v>
       </c>
-      <c r="AH15" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI15" s="6" t="s">
-        <v>225</v>
+      <c r="AH15" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="AI15" s="26" t="s">
+        <v>237</v>
       </c>
       <c r="AK15" s="17"/>
       <c r="AL15" s="17"/>
@@ -3275,11 +3329,11 @@
       <c r="AG16" s="8">
         <v>0</v>
       </c>
-      <c r="AH16" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI16" s="6" t="s">
-        <v>225</v>
+      <c r="AH16" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="AI16" s="29" t="s">
+        <v>239</v>
       </c>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
@@ -3404,11 +3458,11 @@
       <c r="AG17" s="8">
         <v>0</v>
       </c>
-      <c r="AH17" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI17" s="6" t="s">
-        <v>225</v>
+      <c r="AH17" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI17" s="26" t="s">
+        <v>222</v>
       </c>
       <c r="AK17" s="17"/>
       <c r="AL17" s="17"/>
@@ -3533,11 +3587,11 @@
       <c r="AG18" s="8">
         <v>0</v>
       </c>
-      <c r="AH18" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI18" s="6" t="s">
-        <v>225</v>
+      <c r="AH18" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="AI18" s="29" t="s">
+        <v>222</v>
       </c>
       <c r="AK18" s="17"/>
       <c r="AL18" s="17"/>
@@ -3662,11 +3716,11 @@
       <c r="AG19" t="s">
         <v>118</v>
       </c>
-      <c r="AH19" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="AI19" s="29" t="s">
-        <v>224</v>
+      <c r="AH19" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI19" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="AK19" s="17"/>
       <c r="AL19" s="17"/>

--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D4380C-F223-47E9-A718-3BDCEE6D91FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050BB460-B420-4F4C-BE8D-61174CFF70C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
@@ -543,9 +543,6 @@
     <t>【單場最佳陣容與搭檔效益】</t>
   </si>
   <si>
-    <t>【單場焦點對位交鋒 (WOWY: 克雷格 vs 夢想家林俊吉)】</t>
-  </si>
-  <si>
     <t>在場時間</t>
   </si>
   <si>
@@ -754,6 +751,9 @@
   </si>
   <si>
     <t>傷癒復出替補18分鐘三分5中3高效率拿9分4籃板，外圍準星依舊犀利。</t>
+  </si>
+  <si>
+    <t>【單場焦點對位交鋒】</t>
   </si>
 </sst>
 </file>
@@ -1707,13 +1707,13 @@
         <v>1</v>
       </c>
       <c r="AH5" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="AI5" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="AI5" s="26" t="s">
-        <v>218</v>
-      </c>
       <c r="AK5" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AL5" s="25" t="s">
         <v>41</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="AR5" s="16"/>
       <c r="AS5" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AT5" s="30">
         <v>0.52777777777777779</v>
@@ -1754,10 +1754,10 @@
       </c>
       <c r="AY5" s="16"/>
       <c r="AZ5" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BA5" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BB5" s="25">
         <v>-11</v>
@@ -1772,7 +1772,7 @@
         <v>-21.1</v>
       </c>
       <c r="BF5" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -1876,13 +1876,13 @@
         <v>3</v>
       </c>
       <c r="AH6" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="AI6" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="AI6" s="29" t="s">
-        <v>220</v>
-      </c>
       <c r="AK6" s="27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL6" s="28" t="s">
         <v>60</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="AR6" s="16"/>
       <c r="AS6" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AT6" s="31">
         <v>0.30208333333333331</v>
@@ -1923,10 +1923,10 @@
       </c>
       <c r="AY6" s="16"/>
       <c r="AZ6" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BA6" s="28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB6" s="28">
         <v>8</v>
@@ -1941,7 +1941,7 @@
         <v>15.1</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -2045,13 +2045,13 @@
         <v>0</v>
       </c>
       <c r="AH7" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="AI7" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="AI7" s="26" t="s">
-        <v>222</v>
-      </c>
       <c r="AK7" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL7" s="25" t="s">
         <v>50</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="AR7" s="16"/>
       <c r="AS7" s="24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AT7" s="30">
         <v>0.28472222222222221</v>
@@ -2092,10 +2092,10 @@
       </c>
       <c r="AY7" s="16"/>
       <c r="AZ7" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BA7" s="25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BB7" s="25">
         <v>-3</v>
@@ -2110,7 +2110,7 @@
         <v>-17.7</v>
       </c>
       <c r="BF7" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -2214,10 +2214,10 @@
         <v>0.5</v>
       </c>
       <c r="AH8" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AI8" s="29" t="s">
         <v>223</v>
-      </c>
-      <c r="AI8" s="29" t="s">
-        <v>224</v>
       </c>
       <c r="AK8" s="27" t="s">
         <v>114</v>
@@ -2357,13 +2357,13 @@
         <v>0</v>
       </c>
       <c r="AH9" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="AI9" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="AI9" s="26" t="s">
-        <v>226</v>
-      </c>
       <c r="AK9" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL9" s="25" t="s">
         <v>85</v>
@@ -2500,13 +2500,13 @@
         <v>2</v>
       </c>
       <c r="AH10" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="AI10" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="AI10" s="29" t="s">
-        <v>228</v>
-      </c>
       <c r="AK10" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL10" s="28" t="s">
         <v>97</v>
@@ -2643,13 +2643,13 @@
         <v>0</v>
       </c>
       <c r="AH11" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="AI11" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="AI11" s="26" t="s">
-        <v>230</v>
-      </c>
       <c r="AK11" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL11" s="25" t="s">
         <v>74</v>
@@ -2786,13 +2786,13 @@
         <v>3</v>
       </c>
       <c r="AH12" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI12" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="AI12" s="29" t="s">
-        <v>232</v>
-      </c>
       <c r="AK12" s="27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL12" s="28" t="s">
         <v>81</v>
@@ -2929,13 +2929,13 @@
         <v>0</v>
       </c>
       <c r="AH13" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="AI13" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="AI13" s="26" t="s">
-        <v>234</v>
-      </c>
       <c r="AK13" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL13" s="25" t="s">
         <v>66</v>
@@ -3072,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="AH14" s="27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AI14" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AK14" s="17"/>
       <c r="AL14" s="17"/>
@@ -3201,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="AH15" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="AI15" s="26" t="s">
         <v>236</v>
-      </c>
-      <c r="AI15" s="26" t="s">
-        <v>237</v>
       </c>
       <c r="AK15" s="17"/>
       <c r="AL15" s="17"/>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AH16" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="AI16" s="29" t="s">
         <v>238</v>
-      </c>
-      <c r="AI16" s="29" t="s">
-        <v>239</v>
       </c>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
@@ -3459,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="AH17" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AI17" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AK17" s="17"/>
       <c r="AL17" s="17"/>
@@ -3588,10 +3588,10 @@
         <v>0</v>
       </c>
       <c r="AH18" s="27" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AI18" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AK18" s="17"/>
       <c r="AL18" s="17"/>
@@ -3717,10 +3717,10 @@
         <v>118</v>
       </c>
       <c r="AH19" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="AI19" s="26" t="s">
         <v>242</v>
-      </c>
-      <c r="AI19" s="26" t="s">
-        <v>243</v>
       </c>
       <c r="AK19" s="17"/>
       <c r="AL19" s="17"/>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="3" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
       <c r="AK3" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AL3" s="12"/>
       <c r="AM3" s="12"/>
@@ -4754,7 +4754,7 @@
       <c r="AX3" s="12"/>
       <c r="AY3" s="13"/>
       <c r="AZ3" s="12" t="s">
-        <v>173</v>
+        <v>243</v>
       </c>
       <c r="BA3" s="12"/>
     </row>
@@ -4869,32 +4869,32 @@
         <v>3</v>
       </c>
       <c r="AL4" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="AM4" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="AM4" s="14" t="s">
+      <c r="AN4" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="AN4" s="14" t="s">
+      <c r="AO4" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="AO4" s="14" t="s">
+      <c r="AP4" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AP4" s="14" t="s">
+      <c r="AQ4" s="14" t="s">
         <v>178</v>
-      </c>
-      <c r="AQ4" s="14" t="s">
-        <v>179</v>
       </c>
       <c r="AR4" s="15"/>
       <c r="AS4" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AT4" s="14" t="s">
         <v>132</v>
       </c>
       <c r="AU4" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AV4" s="14" t="s">
         <v>165</v>
@@ -4907,10 +4907,10 @@
       </c>
       <c r="AY4" s="15"/>
       <c r="AZ4" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="BA4" s="14" t="s">
         <v>182</v>
-      </c>
-      <c r="BA4" s="14" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.25">
@@ -5017,7 +5017,7 @@
       <c r="AI5" s="22"/>
       <c r="AJ5" s="17"/>
       <c r="AK5" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AL5" s="25" t="s">
         <v>41</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="AR5" s="16"/>
       <c r="AS5" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AT5" s="30">
         <v>0.52777777777777779</v>
@@ -5058,10 +5058,10 @@
       </c>
       <c r="AY5" s="16"/>
       <c r="AZ5" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BA5" s="32" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.25">
@@ -5168,7 +5168,7 @@
       <c r="AI6" s="22"/>
       <c r="AJ6" s="17"/>
       <c r="AK6" s="27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL6" s="28" t="s">
         <v>60</v>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AR6" s="16"/>
       <c r="AS6" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AT6" s="31">
         <v>0.30208333333333331</v>
@@ -5209,10 +5209,10 @@
       </c>
       <c r="AY6" s="16"/>
       <c r="AZ6" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BA6" s="32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.25">
@@ -5319,7 +5319,7 @@
       <c r="AI7" s="22"/>
       <c r="AJ7" s="17"/>
       <c r="AK7" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL7" s="25" t="s">
         <v>50</v>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AR7" s="16"/>
       <c r="AS7" s="24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AT7" s="30">
         <v>0.28472222222222221</v>
@@ -5360,10 +5360,10 @@
       </c>
       <c r="AY7" s="16"/>
       <c r="AZ7" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BA7" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="AR8" s="16"/>
       <c r="AS8" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AT8" s="14"/>
       <c r="AU8" s="20"/>
@@ -5607,7 +5607,7 @@
       <c r="AI9" s="22"/>
       <c r="AJ9" s="17"/>
       <c r="AK9" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL9" s="25" t="s">
         <v>85</v>
@@ -5629,10 +5629,10 @@
       </c>
       <c r="AR9" s="16"/>
       <c r="AS9" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AT9" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AU9" s="25">
         <v>-4</v>
@@ -5754,7 +5754,7 @@
       <c r="AI10" s="22"/>
       <c r="AJ10" s="17"/>
       <c r="AK10" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL10" s="28" t="s">
         <v>97</v>
@@ -5776,10 +5776,10 @@
       </c>
       <c r="AR10" s="16"/>
       <c r="AS10" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AT10" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AU10" s="28">
         <v>-2</v>
@@ -5901,7 +5901,7 @@
       <c r="AI11" s="22"/>
       <c r="AJ11" s="17"/>
       <c r="AK11" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL11" s="25" t="s">
         <v>74</v>
@@ -5923,10 +5923,10 @@
       </c>
       <c r="AR11" s="16"/>
       <c r="AS11" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AT11" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AU11" s="25">
         <v>-11</v>
@@ -6048,7 +6048,7 @@
       <c r="AI12" s="22"/>
       <c r="AJ12" s="17"/>
       <c r="AK12" s="27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL12" s="28" t="s">
         <v>81</v>
@@ -6183,7 +6183,7 @@
       <c r="AI13" s="22"/>
       <c r="AJ13" s="17"/>
       <c r="AK13" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL13" s="25" t="s">
         <v>66</v>

--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北中信特攻.xlsx
@@ -8,21 +8,517 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050BB460-B420-4F4C-BE8D-61174CFF70C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280BF315-9FD1-4FD5-B91D-6B517AE8C285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
-    <sheet name="球員進階數據 (Advanced Stats)" sheetId="3" r:id="rId2"/>
-    <sheet name="2026.10.25 G05 國王 vs 中信特攻" sheetId="2" r:id="rId3"/>
+    <sheet name="球員進階數據 (Advanced Stats)" sheetId="2" r:id="rId2"/>
+    <sheet name="2026.10.25 G05 國王 vs 中信特攻" sheetId="3" r:id="rId3"/>
+    <sheet name="2026.10.25 G06 國王 vs 中信特攻" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="245">
+  <si>
+    <t>新北中信特攻 例行賽單場球員攻守數據表 (81 : 89)</t>
+  </si>
+  <si>
+    <t>註：採計TPBL官方電子紀錄攻守數據。</t>
+  </si>
+  <si>
+    <t>【單場主力 On/Off 淨勝分 (≥ 8分鐘)】</t>
+  </si>
+  <si>
+    <t>【單場最佳陣容與搭檔效益】</t>
+  </si>
+  <si>
+    <t>【單場焦點對位交鋒】</t>
+  </si>
+  <si>
+    <t>背號</t>
+  </si>
+  <si>
+    <t>球員名</t>
+  </si>
+  <si>
+    <t>本土/洋將</t>
+  </si>
+  <si>
+    <t>位置</t>
+  </si>
+  <si>
+    <t>在台年資</t>
+  </si>
+  <si>
+    <t>出賽</t>
+  </si>
+  <si>
+    <t>時間[分]</t>
+  </si>
+  <si>
+    <t>得分</t>
+  </si>
+  <si>
+    <t>投籃命中</t>
+  </si>
+  <si>
+    <t>投籃出手</t>
+  </si>
+  <si>
+    <t>命中%</t>
+  </si>
+  <si>
+    <t>兩分命中</t>
+  </si>
+  <si>
+    <t>兩分出手</t>
+  </si>
+  <si>
+    <t>兩分%</t>
+  </si>
+  <si>
+    <t>三分命中</t>
+  </si>
+  <si>
+    <t>三分出手</t>
+  </si>
+  <si>
+    <t>三分%</t>
+  </si>
+  <si>
+    <t>罰球命中</t>
+  </si>
+  <si>
+    <t>罰球出手</t>
+  </si>
+  <si>
+    <t>罰球%</t>
+  </si>
+  <si>
+    <t>進攻籃板</t>
+  </si>
+  <si>
+    <t>防守籃板</t>
+  </si>
+  <si>
+    <t>籃板</t>
+  </si>
+  <si>
+    <t>助攻</t>
+  </si>
+  <si>
+    <t>抄截</t>
+  </si>
+  <si>
+    <t>阻攻</t>
+  </si>
+  <si>
+    <t>失誤</t>
+  </si>
+  <si>
+    <t>犯規</t>
+  </si>
+  <si>
+    <t>EFF</t>
+  </si>
+  <si>
+    <t>+/-</t>
+  </si>
+  <si>
+    <t>eFG%</t>
+  </si>
+  <si>
+    <t>TS%</t>
+  </si>
+  <si>
+    <t>AST/TO</t>
+  </si>
+  <si>
+    <t>投籃熱區與進攻特徵分佈</t>
+  </si>
+  <si>
+    <t>備註 / 例行賽表現重點</t>
+  </si>
+  <si>
+    <t>在場時間</t>
+  </si>
+  <si>
+    <t>On_ORtg</t>
+  </si>
+  <si>
+    <t>On_DRtg</t>
+  </si>
+  <si>
+    <t>On_NetRtg</t>
+  </si>
+  <si>
+    <t>Off_NetRtg</t>
+  </si>
+  <si>
+    <t>淨影響力(Diff)</t>
+  </si>
+  <si>
+    <t>陣容組合 / 搭檔</t>
+  </si>
+  <si>
+    <t>上場時間</t>
+  </si>
+  <si>
+    <t>正負值(+/-)</t>
+  </si>
+  <si>
+    <t>Lineup ORtg</t>
+  </si>
+  <si>
+    <t>Lineup DRtg</t>
+  </si>
+  <si>
+    <t>Lineup NetRtg</t>
+  </si>
+  <si>
+    <t>對位情境項目</t>
+  </si>
+  <si>
+    <t>攻防表現與命中率變化</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>阿巴西 (Mohammad Al Bachir Gadiaga)</t>
+  </si>
+  <si>
+    <t>本土</t>
+  </si>
+  <si>
+    <t>F/SF</t>
+  </si>
+  <si>
+    <t>5年</t>
+  </si>
+  <si>
+    <t>34:19</t>
+  </si>
+  <si>
+    <t>46.2%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>2.00</t>
+  </si>
+  <si>
+    <t>猛士</t>
+  </si>
+  <si>
+    <t>39:09</t>
+  </si>
+  <si>
+    <t>魏嘉豪-謝亞軒-阿巴西-法拉帝-猛士</t>
+  </si>
+  <si>
+    <t>開局閃電球風與首節狂轟 7 記三分 (Q1 28:17)</t>
+  </si>
+  <si>
+    <t>首節特攻靠著謝亞軒、林韋翰、簡廷兆等射手多點開花，單節三分球 14 投 7 中拉開 11 分領先。</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>李睿麒 (Li Ruei-Ci)</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>6年</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>強斯</t>
+  </si>
+  <si>
+    <t>22:19</t>
+  </si>
+  <si>
+    <t>林韋翰-謝亞軒-阿巴西-強斯-猛士</t>
+  </si>
+  <si>
+    <t>猛士外線手感冰凍與下半場當機 (39:09)</t>
+  </si>
+  <si>
+    <t>猛士全場 21 投僅 3 中（三分球 9 投 0 中）僅拿 6 分；下半場國王收縮防線迫使特攻頻頻遠投打鐵，第三節團隊僅得 14 分遭對手翻盤。</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>魏嘉豪 (Wei Chia-Hao)</t>
+  </si>
+  <si>
+    <t>G/PG</t>
+  </si>
+  <si>
+    <t>26:45</t>
+  </si>
+  <si>
+    <t>33.3%</t>
+  </si>
+  <si>
+    <t>25.0%</t>
+  </si>
+  <si>
+    <t>38.89%</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>謝亞軒</t>
+  </si>
+  <si>
+    <t>30:43</t>
+  </si>
+  <si>
+    <t>魏嘉豪-簡廷兆-林任鴻-法拉帝-強斯</t>
+  </si>
+  <si>
+    <t>單場戰術結論</t>
+  </si>
+  <si>
+    <t>法拉帝禁區繳出 19 分 15 籃板雙十，謝亞軒貢獻 11 分 4 抄截；然而全場失誤達 17 次且下半場外線徹底失靈（後兩節三分球合計 21 投 5 中），主場慘遭逆轉。</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>謝亞軒 (Hsieh Ya-Hsuan)</t>
+  </si>
+  <si>
+    <t>G/SG</t>
+  </si>
+  <si>
+    <t>44.4%</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>37.5%</t>
+  </si>
+  <si>
+    <t>61.11%</t>
+  </si>
+  <si>
+    <t>林韋翰</t>
+  </si>
+  <si>
+    <t>17:37</t>
+  </si>
+  <si>
+    <t>核心搭檔效益 (Key Pairs)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>林任鴻 (Lin Jen-Hung)</t>
+  </si>
+  <si>
+    <t>10年</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>50.00%</t>
+  </si>
+  <si>
+    <t>魏嘉豪</t>
+  </si>
+  <si>
+    <t>謝亞軒 + 阿巴西 (本土雙槍核心)</t>
+  </si>
+  <si>
+    <t>26:30</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>曾信武 (Tseng Hsin-Wu)</t>
+  </si>
+  <si>
+    <t>2年</t>
+  </si>
+  <si>
+    <t>林任鴻</t>
+  </si>
+  <si>
+    <t>魏嘉豪 + 謝亞軒 (外線導傳搭檔)</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>75.00%</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>阿巴西</t>
+  </si>
+  <si>
+    <t>法拉帝 + 猛士 (先發雙洋組合)</t>
+  </si>
+  <si>
+    <t>24:50</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>強斯 (Marvin Jones)</t>
+  </si>
+  <si>
+    <t>洋將</t>
+  </si>
+  <si>
+    <t>PF/C</t>
+  </si>
+  <si>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>18.75%</t>
+  </si>
+  <si>
+    <t>28.15%</t>
+  </si>
+  <si>
+    <t>簡廷兆</t>
+  </si>
+  <si>
+    <t>18:46</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>法拉帝 (Vladimír Brodziansky)</t>
+  </si>
+  <si>
+    <t>第1年</t>
+  </si>
+  <si>
+    <t>32:46</t>
+  </si>
+  <si>
+    <t>66.7%</t>
+  </si>
+  <si>
+    <t>62.5%</t>
+  </si>
+  <si>
+    <t>58.33%</t>
+  </si>
+  <si>
+    <t>61.21%</t>
+  </si>
+  <si>
+    <t>法拉帝</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>黃泓瀚</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>簡廷兆 (Jian Ting-Jhao)</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>4年</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>猛士 (Clay Mounce)</t>
+  </si>
+  <si>
+    <t>14.3%</t>
+  </si>
+  <si>
+    <t>14.29%</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>曾文鼎 (Tseng Wen-Ting)</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>24年</t>
+  </si>
+  <si>
+    <t>01:46</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>李沛澄 (Li Pei-Cheng)</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
   <si>
     <t>2026-2027 賽季 新北中信特攻 (TPBL) 例行賽球員攻守數據表 - 平均數據 (待賽程展開)</t>
   </si>
@@ -30,382 +526,163 @@
     <t>註：採計TPBL 2026-2027 例行賽官方電子紀錄攻守數據。截至2026年10月18日特攻尚未出賽，先列入完整註冊名單與數據架構。</t>
   </si>
   <si>
-    <t>背號</t>
-  </si>
-  <si>
-    <t>球員名</t>
-  </si>
-  <si>
-    <t>本土/洋將</t>
-  </si>
-  <si>
-    <t>位置</t>
-  </si>
-  <si>
-    <t>在台年資</t>
-  </si>
-  <si>
-    <t>出賽</t>
-  </si>
-  <si>
-    <t>時間[分]</t>
-  </si>
-  <si>
-    <t>得分</t>
-  </si>
-  <si>
-    <t>投籃命中</t>
-  </si>
-  <si>
-    <t>投籃出手</t>
-  </si>
-  <si>
-    <t>命中%</t>
-  </si>
-  <si>
-    <t>兩分命中</t>
-  </si>
-  <si>
-    <t>兩分出手</t>
-  </si>
-  <si>
-    <t>兩分%</t>
-  </si>
-  <si>
-    <t>三分命中</t>
-  </si>
-  <si>
-    <t>三分出手</t>
-  </si>
-  <si>
-    <t>三分%</t>
-  </si>
-  <si>
-    <t>罰球命中</t>
-  </si>
-  <si>
-    <t>罰球出手</t>
-  </si>
-  <si>
-    <t>罰球%</t>
-  </si>
-  <si>
-    <t>進攻籃板</t>
-  </si>
-  <si>
-    <t>防守籃板</t>
-  </si>
-  <si>
-    <t>籃板</t>
-  </si>
-  <si>
-    <t>助攻</t>
-  </si>
-  <si>
-    <t>抄截</t>
-  </si>
-  <si>
-    <t>阻攻</t>
-  </si>
-  <si>
-    <t>失誤</t>
-  </si>
-  <si>
-    <t>犯規</t>
-  </si>
-  <si>
-    <t>EFF</t>
-  </si>
-  <si>
-    <t>+/-</t>
-  </si>
-  <si>
-    <t>eFG%</t>
-  </si>
-  <si>
-    <t>TS%</t>
-  </si>
-  <si>
-    <t>AST/TO</t>
-  </si>
-  <si>
-    <t>投籃熱區與進攻特徵分佈</t>
-  </si>
-  <si>
-    <t>備註 / 例行賽表現重點</t>
-  </si>
-  <si>
-    <t>猛士 (Clay Mounce)</t>
-  </si>
-  <si>
-    <t>洋將</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>第1年</t>
-  </si>
-  <si>
-    <t>39:09</t>
-  </si>
-  <si>
-    <t>14.3%</t>
-  </si>
-  <si>
-    <t>25.0%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>14.29%</t>
-  </si>
-  <si>
-    <t>謝亞軒 (Hsieh Ya-Hsuan)</t>
-  </si>
-  <si>
-    <t>本土</t>
-  </si>
-  <si>
-    <t>G/SG</t>
-  </si>
-  <si>
-    <t>5年</t>
-  </si>
-  <si>
-    <t>30:43</t>
-  </si>
-  <si>
-    <t>44.4%</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>37.5%</t>
-  </si>
-  <si>
-    <t>61.11%</t>
+    <t>【賽季累積主力 On/Off 總榜 (全季累計加權)】</t>
+  </si>
+  <si>
+    <t>【賽季最佳五人陣容 (≥ 10分鐘)】</t>
+  </si>
+  <si>
+    <t>【賽季雙洋將化學效應矩陣】</t>
+  </si>
+  <si>
+    <t>累計在場時間</t>
+  </si>
+  <si>
+    <t>累計On_ORtg</t>
+  </si>
+  <si>
+    <t>累計On_DRtg</t>
+  </si>
+  <si>
+    <t>累計On_NetRtg</t>
+  </si>
+  <si>
+    <t>累計Off_NetRtg</t>
+  </si>
+  <si>
+    <t>賽季淨影響力(Diff)</t>
+  </si>
+  <si>
+    <t>五人陣容組合</t>
+  </si>
+  <si>
+    <t>賽季累計時間</t>
+  </si>
+  <si>
+    <t>累計正負值(+/-)</t>
+  </si>
+  <si>
+    <t>洋將搭檔組合</t>
+  </si>
+  <si>
+    <t>共同時間</t>
+  </si>
+  <si>
+    <t>累計(+/-)</t>
+  </si>
+  <si>
+    <t>攻守特徵與搭配建議</t>
+  </si>
+  <si>
+    <t>面框強攻與外線投射(外圍出手佔比43%)</t>
+  </si>
+  <si>
+    <t>首戰外線手感低迷繳6分6板3阻攻，具備高機動性與護框能力，待找回投籃手感。</t>
+  </si>
+  <si>
+    <t>法拉帝 + 猛士</t>
+  </si>
+  <si>
+    <t>空間型前鋒搭檔，但外線失準時禁區容易陷入肉搏，協防移動步幅偏大。</t>
+  </si>
+  <si>
+    <t>外線定點投射(三分佔比89%)</t>
+  </si>
+  <si>
+    <t>首秀飆進3記三分挹注11分4抄截3助攻，特攻外圍第一射手兼第一線外線大鎖。</t>
+  </si>
+  <si>
+    <t>強斯 + 猛士</t>
+  </si>
+  <si>
+    <t>14:19</t>
+  </si>
+  <si>
+    <t>強斯提供扎實禁區卡位與阻攻威嚇，能有效分擔猛士內線防守壓力。</t>
   </si>
   <si>
     <t>奈迪 (Nedim)</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>強斯 (Marvin Jones)</t>
-  </si>
-  <si>
-    <t>PF/C</t>
-  </si>
-  <si>
-    <t>2年</t>
-  </si>
-  <si>
-    <t>22:19</t>
-  </si>
-  <si>
-    <t>12.5%</t>
-  </si>
-  <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>18.75%</t>
-  </si>
-  <si>
-    <t>28.15%</t>
-  </si>
-  <si>
-    <t>法拉帝 (Vladimír Brodziansky)</t>
-  </si>
-  <si>
-    <t>32:46</t>
-  </si>
-  <si>
-    <t>66.7%</t>
-  </si>
-  <si>
-    <t>33.3%</t>
-  </si>
-  <si>
-    <t>62.5%</t>
-  </si>
-  <si>
-    <t>58.33%</t>
-  </si>
-  <si>
-    <t>61.21%</t>
-  </si>
-  <si>
-    <t>阿巴西 (Mohammad Al Bachir Gadiaga)</t>
-  </si>
-  <si>
-    <t>F/SF</t>
-  </si>
-  <si>
-    <t>34:19</t>
-  </si>
-  <si>
-    <t>46.2%</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>53.85%</t>
-  </si>
-  <si>
-    <t>簡廷兆 (Jian Ting-Jhao)</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>4年</t>
-  </si>
-  <si>
-    <t>18:46</t>
-  </si>
-  <si>
-    <t>50.00%</t>
-  </si>
-  <si>
-    <t>魏嘉豪 (Wei Chia-Hao)</t>
-  </si>
-  <si>
-    <t>G/PG</t>
-  </si>
-  <si>
-    <t>26:45</t>
-  </si>
-  <si>
-    <t>38.89%</t>
-  </si>
-  <si>
-    <t>李沛澄 (Li Pei-Cheng)</t>
-  </si>
-  <si>
-    <t>07:43</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>曾信武 (Tseng Hsin-Wu)</t>
-  </si>
-  <si>
-    <t>曾文鼎 (Tseng Wen-Ting)</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>24年</t>
-  </si>
-  <si>
-    <t>01:46</t>
-  </si>
-  <si>
-    <t>林任鴻 (Lin Jen-Hung)</t>
-  </si>
-  <si>
-    <t>10年</t>
-  </si>
-  <si>
-    <t>08:07</t>
-  </si>
-  <si>
-    <t>李睿麒 (Li Ruei-Ci)</t>
-  </si>
-  <si>
-    <t>6年</t>
+    <t>禁區護框洋將(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>待例行賽賽程展開 / 先列入註冊名單與數據架構。</t>
+  </si>
+  <si>
+    <t>法拉帝 + 強斯</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>雙塔配置高度充足，但側翼機動性與反擊退防速度略顯不足。</t>
+  </si>
+  <si>
+    <t>禁區護框與卡位衝搶(前場籃板意識強)</t>
+  </si>
+  <si>
+    <t>首戰抓下9籃板(含4前場板)得5分，提供扎實內線卡位與籃板屏障。</t>
+  </si>
+  <si>
+    <t>內外兼修(兩分50% / 三分50%)，多點分佈</t>
+  </si>
+  <si>
+    <t>首秀狂砍19分15籃板(5前板)大號雙十，內線終結極高效率，特攻攻守真核。</t>
+  </si>
+  <si>
+    <t>轉換快攻與切入突破(衝擊籃框為主)</t>
+  </si>
+  <si>
+    <t>首戰貢獻14分4抄截4助攻，閃電快攻箭頭，具備頂級快攻推進與抄截威脅。</t>
+  </si>
+  <si>
+    <t>外線冷箭與突分(三分命中率50%)</t>
+  </si>
+  <si>
+    <t>替補19分鐘命中2記三分得6分2籃板，二陣外圍具備隨插即用的得分爆發力。</t>
+  </si>
+  <si>
+    <t>擋拆推進與全場導傳(助攻失誤比3.0)</t>
+  </si>
+  <si>
+    <t>先發主控繳出7分6助攻5籃板3抄截，流暢掌控快節奏推進與外圍導傳。</t>
+  </si>
+  <si>
+    <t>外線定點射手(外圍拉開空間)</t>
+  </si>
+  <si>
+    <t>替補出戰8分鐘出手2記三分未果，球隊純射手輪替，負責側翼空間牽制。</t>
+  </si>
+  <si>
+    <t>側翼防守射手(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>高位策應與禁區軸心(傳球視野開闊)</t>
+  </si>
+  <si>
+    <t>出賽近2分鐘主要提供高位戰術策應與防守掩護，老將經驗穩定軍心。</t>
+  </si>
+  <si>
+    <t>空手走位與快攻終結(兩分佔比100%)</t>
+  </si>
+  <si>
+    <t>替補8分鐘兩分4中2得4分2籃板，跑動積極，提供側翼扎實空切活力。</t>
+  </si>
+  <si>
+    <t>外線砲塔射手(待例行賽出賽)</t>
   </si>
   <si>
     <t>余維豪 (Yu Wei-Hao)</t>
   </si>
   <si>
-    <t>新北中信特攻 例行賽單場球員攻守數據表 (81 : 89)</t>
-  </si>
-  <si>
-    <t>註：採計TPBL官方電子紀錄攻守數據。</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2.00</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>3.00</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>林韋翰</t>
-  </si>
-  <si>
-    <t>17:37</t>
-  </si>
-  <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>75.00%</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>黃泓瀚</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>77</t>
+    <t>替補控衛組織(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>陣地戰指揮官與外線跳投(三分命中率60%)</t>
+  </si>
+  <si>
+    <t>傷癒復出替補18分鐘三分5中3高效率拿9分4籃板，外圍準星依舊犀利。</t>
   </si>
   <si>
     <t>新北中信特攻 球員進階數據統計表 (Advanced Stats)</t>
@@ -420,9 +697,6 @@
     <t>身分</t>
   </si>
   <si>
-    <t>上場時間</t>
-  </si>
-  <si>
     <t>場均得分</t>
   </si>
   <si>
@@ -483,277 +757,7 @@
     <t>25.5%</t>
   </si>
   <si>
-    <t>【賽季累積主力 On/Off 總榜 (全季累計加權)】</t>
-  </si>
-  <si>
-    <t>【賽季最佳五人陣容 (≥ 10分鐘)】</t>
-  </si>
-  <si>
-    <t>【賽季雙洋將化學效應矩陣】</t>
-  </si>
-  <si>
-    <t>累計在場時間</t>
-  </si>
-  <si>
-    <t>累計On_ORtg</t>
-  </si>
-  <si>
-    <t>累計On_DRtg</t>
-  </si>
-  <si>
-    <t>累計On_NetRtg</t>
-  </si>
-  <si>
-    <t>累計Off_NetRtg</t>
-  </si>
-  <si>
-    <t>賽季淨影響力(Diff)</t>
-  </si>
-  <si>
-    <t>五人陣容組合</t>
-  </si>
-  <si>
-    <t>賽季累計時間</t>
-  </si>
-  <si>
-    <t>累計正負值(+/-)</t>
-  </si>
-  <si>
-    <t>Lineup ORtg</t>
-  </si>
-  <si>
-    <t>Lineup DRtg</t>
-  </si>
-  <si>
-    <t>Lineup NetRtg</t>
-  </si>
-  <si>
-    <t>洋將搭檔組合</t>
-  </si>
-  <si>
-    <t>共同時間</t>
-  </si>
-  <si>
-    <t>累計(+/-)</t>
-  </si>
-  <si>
-    <t>攻守特徵與搭配建議</t>
-  </si>
-  <si>
-    <t>【單場最佳陣容與搭檔效益】</t>
-  </si>
-  <si>
-    <t>在場時間</t>
-  </si>
-  <si>
-    <t>On_ORtg</t>
-  </si>
-  <si>
-    <t>On_DRtg</t>
-  </si>
-  <si>
-    <t>On_NetRtg</t>
-  </si>
-  <si>
-    <t>Off_NetRtg</t>
-  </si>
-  <si>
-    <t>淨影響力(Diff)</t>
-  </si>
-  <si>
-    <t>陣容組合 / 搭檔</t>
-  </si>
-  <si>
-    <t>正負值(+/-)</t>
-  </si>
-  <si>
-    <t>對位情境項目</t>
-  </si>
-  <si>
-    <t>攻防表現與命中率變化</t>
-  </si>
-  <si>
-    <t>單場戰術結論</t>
-  </si>
-  <si>
-    <t>核心搭檔效益 (Key Pairs)</t>
-  </si>
-  <si>
-    <t>【單場主力 On/Off 淨勝分 (≥ 8分鐘)】</t>
-  </si>
-  <si>
-    <t>猛士</t>
-  </si>
-  <si>
-    <t>強斯</t>
-  </si>
-  <si>
-    <t>謝亞軒</t>
-  </si>
-  <si>
-    <t>魏嘉豪</t>
-  </si>
-  <si>
-    <t>林任鴻</t>
-  </si>
-  <si>
-    <t>阿巴西</t>
-  </si>
-  <si>
-    <t>簡廷兆</t>
-  </si>
-  <si>
-    <t>法拉帝</t>
-  </si>
-  <si>
-    <t>魏嘉豪-謝亞軒-阿巴西-法拉帝-猛士</t>
-  </si>
-  <si>
-    <t>林韋翰-謝亞軒-阿巴西-強斯-猛士</t>
-  </si>
-  <si>
-    <t>魏嘉豪-簡廷兆-林任鴻-法拉帝-強斯</t>
-  </si>
-  <si>
-    <t>26:30</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>24:50</t>
-  </si>
-  <si>
-    <t>謝亞軒 + 阿巴西 (本土雙槍核心)</t>
-  </si>
-  <si>
-    <t>魏嘉豪 + 謝亞軒 (外線導傳搭檔)</t>
-  </si>
-  <si>
-    <t>法拉帝 + 猛士 (先發雙洋組合)</t>
-  </si>
-  <si>
-    <t>開局閃電球風與首節狂轟 7 記三分 (Q1 28:17)</t>
-  </si>
-  <si>
-    <t>猛士外線手感冰凍與下半場當機 (39:09)</t>
-  </si>
-  <si>
-    <t>首節特攻靠著謝亞軒、林韋翰、簡廷兆等射手多點開花，單節三分球 14 投 7 中拉開 11 分領先。</t>
-  </si>
-  <si>
-    <t>猛士全場 21 投僅 3 中（三分球 9 投 0 中）僅拿 6 分；下半場國王收縮防線迫使特攻頻頻遠投打鐵，第三節團隊僅得 14 分遭對手翻盤。</t>
-  </si>
-  <si>
-    <t>法拉帝禁區繳出 19 分 15 籃板雙十，謝亞軒貢獻 11 分 4 抄截；然而全場失誤達 17 次且下半場外線徹底失靈（後兩節三分球合計 21 投 5 中），主場慘遭逆轉。</t>
-  </si>
-  <si>
-    <t>空間型前鋒搭檔，但外線失準時禁區容易陷入肉搏，協防移動步幅偏大。</t>
-  </si>
-  <si>
-    <t>14:19</t>
-  </si>
-  <si>
-    <t>強斯提供扎實禁區卡位與阻攻威嚇，能有效分擔猛士內線防守壓力。</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>雙塔配置高度充足，但側翼機動性與反擊退防速度略顯不足。</t>
-  </si>
-  <si>
-    <t>法拉帝 + 猛士</t>
-  </si>
-  <si>
-    <t>強斯 + 猛士</t>
-  </si>
-  <si>
-    <t>法拉帝 + 強斯</t>
-  </si>
-  <si>
-    <t>面框強攻與外線投射(外圍出手佔比43%)</t>
-  </si>
-  <si>
-    <t>首戰外線手感低迷繳6分6板3阻攻，具備高機動性與護框能力，待找回投籃手感。</t>
-  </si>
-  <si>
-    <t>外線定點投射(三分佔比89%)</t>
-  </si>
-  <si>
-    <t>首秀飆進3記三分挹注11分4抄截3助攻，特攻外圍第一射手兼第一線外線大鎖。</t>
-  </si>
-  <si>
-    <t>禁區護框洋將(待例行賽出賽)</t>
-  </si>
-  <si>
-    <t>待例行賽賽程展開 / 先列入註冊名單與數據架構。</t>
-  </si>
-  <si>
-    <t>禁區護框與卡位衝搶(前場籃板意識強)</t>
-  </si>
-  <si>
-    <t>首戰抓下9籃板(含4前場板)得5分，提供扎實內線卡位與籃板屏障。</t>
-  </si>
-  <si>
-    <t>內外兼修(兩分50% / 三分50%)，多點分佈</t>
-  </si>
-  <si>
-    <t>首秀狂砍19分15籃板(5前板)大號雙十，內線終結極高效率，特攻攻守真核。</t>
-  </si>
-  <si>
-    <t>轉換快攻與切入突破(衝擊籃框為主)</t>
-  </si>
-  <si>
-    <t>首戰貢獻14分4抄截4助攻，閃電快攻箭頭，具備頂級快攻推進與抄截威脅。</t>
-  </si>
-  <si>
-    <t>外線冷箭與突分(三分命中率50%)</t>
-  </si>
-  <si>
-    <t>替補19分鐘命中2記三分得6分2籃板，二陣外圍具備隨插即用的得分爆發力。</t>
-  </si>
-  <si>
-    <t>擋拆推進與全場導傳(助攻失誤比3.0)</t>
-  </si>
-  <si>
-    <t>先發主控繳出7分6助攻5籃板3抄截，流暢掌控快節奏推進與外圍導傳。</t>
-  </si>
-  <si>
-    <t>外線定點射手(外圍拉開空間)</t>
-  </si>
-  <si>
-    <t>替補出戰8分鐘出手2記三分未果，球隊純射手輪替，負責側翼空間牽制。</t>
-  </si>
-  <si>
-    <t>側翼防守射手(待例行賽出賽)</t>
-  </si>
-  <si>
-    <t>高位策應與禁區軸心(傳球視野開闊)</t>
-  </si>
-  <si>
-    <t>出賽近2分鐘主要提供高位戰術策應與防守掩護，老將經驗穩定軍心。</t>
-  </si>
-  <si>
-    <t>空手走位與快攻終結(兩分佔比100%)</t>
-  </si>
-  <si>
-    <t>替補8分鐘兩分4中2得4分2籃板，跑動積極，提供側翼扎實空切活力。</t>
-  </si>
-  <si>
-    <t>外線砲塔射手(待例行賽出賽)</t>
-  </si>
-  <si>
-    <t>替補控衛組織(待例行賽出賽)</t>
-  </si>
-  <si>
-    <t>陣地戰指揮官與外線跳投(三分命中率60%)</t>
-  </si>
-  <si>
-    <t>傷癒復出替補18分鐘三分5中3高效率拿9分4籃板，外圍準星依舊犀利。</t>
-  </si>
-  <si>
-    <t>【單場焦點對位交鋒】</t>
+    <t>【單場焦點對位交鋒 (WOWY: 克雷格 vs 夢想家林俊吉)】</t>
   </si>
 </sst>
 </file>
@@ -949,7 +953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1007,6 +1011,40 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1287,7 +1325,7 @@
   <sheetData>
     <row r="1" spans="1:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1348,7 +1386,7 @@
     </row>
     <row r="2" spans="1:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1407,9 +1445,9 @@
       <c r="BE2" s="11"/>
       <c r="BF2" s="11"/>
     </row>
-    <row r="3" spans="1:58" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:58" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AK3" s="19" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="AL3" s="12"/>
       <c r="AM3" s="12"/>
@@ -1419,7 +1457,7 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="12" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="AT3" s="12"/>
       <c r="AU3" s="12"/>
@@ -1428,7 +1466,7 @@
       <c r="AX3" s="12"/>
       <c r="AY3" s="13"/>
       <c r="AZ3" s="12" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="BA3" s="12"/>
       <c r="BB3" s="12"/>
@@ -1437,196 +1475,196 @@
       <c r="BE3" s="12"/>
       <c r="BF3" s="12"/>
     </row>
-    <row r="4" spans="1:58" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:58" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK4" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="AL4" s="14" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="AM4" s="14" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="AN4" s="14" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="AO4" s="14" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="AP4" s="14" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="AQ4" s="14" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="AR4" s="15"/>
       <c r="AS4" s="14" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="AT4" s="14" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AU4" s="14" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AV4" s="14" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="AW4" s="14" t="s">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="AX4" s="14" t="s">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="AY4" s="15"/>
       <c r="AZ4" s="14" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="BA4" s="14" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="BB4" s="14" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="BC4" s="14" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="BD4" s="14" t="s">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="BE4" s="14" t="s">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="BF4" s="14" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>61</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="F5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="H5" s="8">
         <v>6</v>
@@ -1638,7 +1676,7 @@
         <v>21</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="L5" s="8">
         <v>3</v>
@@ -1647,7 +1685,7 @@
         <v>12</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="O5" s="8">
         <v>0</v>
@@ -1656,7 +1694,7 @@
         <v>9</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R5" s="8">
         <v>0</v>
@@ -1665,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U5" s="8">
         <v>4</v>
@@ -1698,25 +1736,25 @@
         <v>-3</v>
       </c>
       <c r="AE5" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="AF5" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="AG5" s="8">
         <v>1</v>
       </c>
       <c r="AH5" s="24" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="AI5" s="26" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="AK5" s="24" t="s">
-        <v>186</v>
+        <v>66</v>
       </c>
       <c r="AL5" s="25" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="AM5" s="25">
         <v>86.8</v>
@@ -1735,7 +1773,7 @@
       </c>
       <c r="AR5" s="16"/>
       <c r="AS5" s="24" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="AT5" s="30">
         <v>0.52777777777777779</v>
@@ -1754,10 +1792,10 @@
       </c>
       <c r="AY5" s="16"/>
       <c r="AZ5" s="17" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="BA5" s="25" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="BB5" s="25">
         <v>-11</v>
@@ -1772,30 +1810,30 @@
         <v>-21.1</v>
       </c>
       <c r="BF5" s="26" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>10</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="H6" s="8">
         <v>11</v>
@@ -1807,7 +1845,7 @@
         <v>9</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -1816,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="O6" s="8">
         <v>3</v>
@@ -1825,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="R6" s="8">
         <v>0</v>
@@ -1834,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U6" s="8">
         <v>1</v>
@@ -1867,25 +1905,25 @@
         <v>-3</v>
       </c>
       <c r="AE6" s="9" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="AF6" s="9" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="AG6" s="8">
         <v>3</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="AI6" s="29" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="AL6" s="28" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AM6" s="28">
         <v>90</v>
@@ -1904,7 +1942,7 @@
       </c>
       <c r="AR6" s="16"/>
       <c r="AS6" s="27" t="s">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="AT6" s="31">
         <v>0.30208333333333331</v>
@@ -1923,10 +1961,10 @@
       </c>
       <c r="AY6" s="16"/>
       <c r="AZ6" s="17" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="BA6" s="28" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="BB6" s="28">
         <v>8</v>
@@ -1941,24 +1979,24 @@
         <v>15.1</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>28</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -1976,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="L7" s="8">
         <v>0</v>
@@ -1985,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="O7" s="8">
         <v>0</v>
@@ -1994,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="R7" s="8">
         <v>0</v>
@@ -2003,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="U7" s="8">
         <v>0</v>
@@ -2033,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="AE7" s="9">
         <v>0</v>
@@ -2045,16 +2083,16 @@
         <v>0</v>
       </c>
       <c r="AH7" s="24" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="AI7" s="26" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="AK7" s="24" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="AL7" s="25" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="AM7" s="25">
         <v>86.2</v>
@@ -2073,7 +2111,7 @@
       </c>
       <c r="AR7" s="16"/>
       <c r="AS7" s="24" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="AT7" s="30">
         <v>0.28472222222222221</v>
@@ -2092,10 +2130,10 @@
       </c>
       <c r="AY7" s="16"/>
       <c r="AZ7" s="17" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="BA7" s="25" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="BB7" s="25">
         <v>-3</v>
@@ -2110,30 +2148,30 @@
         <v>-17.7</v>
       </c>
       <c r="BF7" s="26" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>17</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H8" s="8">
         <v>5</v>
@@ -2145,7 +2183,7 @@
         <v>8</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="L8" s="8">
         <v>0</v>
@@ -2154,7 +2192,7 @@
         <v>6</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O8" s="8">
         <v>1</v>
@@ -2163,7 +2201,7 @@
         <v>2</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R8" s="8">
         <v>2</v>
@@ -2172,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="U8" s="8">
         <v>4</v>
@@ -2205,25 +2243,25 @@
         <v>1</v>
       </c>
       <c r="AE8" s="9" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="AF8" s="9" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="AG8" s="8">
         <v>0.5</v>
       </c>
       <c r="AH8" s="27" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="AI8" s="29" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="AK8" s="27" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AL8" s="28" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AM8" s="28">
         <v>85.8</v>
@@ -2256,27 +2294,27 @@
       <c r="BE8" s="17"/>
       <c r="BF8" s="17"/>
     </row>
-    <row r="9" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>20</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="F9" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="H9" s="8">
         <v>19</v>
@@ -2288,7 +2326,7 @@
         <v>12</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L9" s="8">
         <v>4</v>
@@ -2297,7 +2335,7 @@
         <v>6</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="O9" s="8">
         <v>2</v>
@@ -2306,7 +2344,7 @@
         <v>6</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="R9" s="8">
         <v>5</v>
@@ -2315,7 +2353,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="U9" s="8">
         <v>5</v>
@@ -2348,25 +2386,25 @@
         <v>-14</v>
       </c>
       <c r="AE9" s="9" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="AF9" s="9" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="AG9" s="8">
         <v>0</v>
       </c>
       <c r="AH9" s="24" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="AI9" s="26" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="AK9" s="24" t="s">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="AL9" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AM9" s="25">
         <v>83.9</v>
@@ -2399,27 +2437,27 @@
       <c r="BE9" s="17"/>
       <c r="BF9" s="17"/>
     </row>
-    <row r="10" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F10" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="H10" s="8">
         <v>14</v>
@@ -2431,7 +2469,7 @@
         <v>13</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L10" s="8">
         <v>4</v>
@@ -2440,7 +2478,7 @@
         <v>8</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O10" s="8">
         <v>2</v>
@@ -2449,7 +2487,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -2458,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U10" s="8">
         <v>0</v>
@@ -2491,25 +2529,25 @@
         <v>-8</v>
       </c>
       <c r="AE10" s="9" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="AF10" s="9" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="AG10" s="8">
         <v>2</v>
       </c>
       <c r="AH10" s="27" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="AI10" s="29" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="AK10" s="27" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="AL10" s="28" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AM10" s="28">
         <v>82.3</v>
@@ -2542,27 +2580,27 @@
       <c r="BE10" s="17"/>
       <c r="BF10" s="17"/>
     </row>
-    <row r="11" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="F11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="H11" s="8">
         <v>6</v>
@@ -2574,7 +2612,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
@@ -2583,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O11" s="8">
         <v>2</v>
@@ -2592,7 +2630,7 @@
         <v>4</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R11" s="8">
         <v>0</v>
@@ -2601,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U11" s="8">
         <v>0</v>
@@ -2634,25 +2672,25 @@
         <v>-8</v>
       </c>
       <c r="AE11" s="9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AF11" s="9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AG11" s="8">
         <v>0</v>
       </c>
       <c r="AH11" s="24" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="AI11" s="26" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="AK11" s="24" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="AL11" s="25" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="AM11" s="25">
         <v>82.7</v>
@@ -2685,27 +2723,27 @@
       <c r="BE11" s="17"/>
       <c r="BF11" s="17"/>
     </row>
-    <row r="12" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" s="8">
         <v>7</v>
@@ -2717,7 +2755,7 @@
         <v>9</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L12" s="8">
         <v>2</v>
@@ -2726,7 +2764,7 @@
         <v>5</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="O12" s="8">
         <v>1</v>
@@ -2735,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="R12" s="8">
         <v>0</v>
@@ -2744,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U12" s="8">
         <v>0</v>
@@ -2777,25 +2815,25 @@
         <v>-5</v>
       </c>
       <c r="AE12" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AF12" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AG12" s="8">
         <v>3</v>
       </c>
       <c r="AH12" s="27" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="AI12" s="29" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="AK12" s="27" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="AL12" s="28" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="AM12" s="28">
         <v>77.599999999999994</v>
@@ -2828,27 +2866,27 @@
       <c r="BE12" s="17"/>
       <c r="BF12" s="17"/>
     </row>
-    <row r="13" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>77</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="H13" s="8">
         <v>0</v>
@@ -2860,7 +2898,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
@@ -2869,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
@@ -2878,7 +2916,7 @@
         <v>2</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -2887,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U13" s="8">
         <v>0</v>
@@ -2920,25 +2958,25 @@
         <v>4</v>
       </c>
       <c r="AE13" s="9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AF13" s="9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AG13" s="8">
         <v>0</v>
       </c>
       <c r="AH13" s="24" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="AI13" s="26" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="AK13" s="24" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="AL13" s="25" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="AM13" s="25">
         <v>77.599999999999994</v>
@@ -2971,21 +3009,21 @@
       <c r="BE13" s="17"/>
       <c r="BF13" s="17"/>
     </row>
-    <row r="14" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>14</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F14" s="5">
         <v>0</v>
@@ -3003,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
@@ -3012,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="O14" s="8">
         <v>0</v>
@@ -3021,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="R14" s="8">
         <v>0</v>
@@ -3030,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="U14" s="8">
         <v>0</v>
@@ -3060,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="AE14" s="9">
         <v>0</v>
@@ -3072,10 +3110,10 @@
         <v>0</v>
       </c>
       <c r="AH14" s="27" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="AI14" s="29" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="AK14" s="17"/>
       <c r="AL14" s="17"/>
@@ -3100,27 +3138,27 @@
       <c r="BE14" s="17"/>
       <c r="BF14" s="17"/>
     </row>
-    <row r="15" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>76</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="F15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="H15" s="8">
         <v>0</v>
@@ -3132,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
@@ -3141,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O15" s="8">
         <v>0</v>
@@ -3150,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R15" s="8">
         <v>0</v>
@@ -3159,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U15" s="8">
         <v>0</v>
@@ -3192,19 +3230,19 @@
         <v>0</v>
       </c>
       <c r="AE15" s="9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AF15" s="9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AG15" s="8">
         <v>0</v>
       </c>
       <c r="AH15" s="24" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="AI15" s="26" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="AK15" s="17"/>
       <c r="AL15" s="17"/>
@@ -3229,27 +3267,27 @@
       <c r="BE15" s="17"/>
       <c r="BF15" s="17"/>
     </row>
-    <row r="16" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H16" s="8">
         <v>4</v>
@@ -3261,7 +3299,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L16" s="8">
         <v>2</v>
@@ -3270,7 +3308,7 @@
         <v>4</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O16" s="8">
         <v>0</v>
@@ -3279,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>
@@ -3288,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U16" s="8">
         <v>2</v>
@@ -3321,19 +3359,19 @@
         <v>-2</v>
       </c>
       <c r="AE16" s="9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AF16" s="9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AG16" s="8">
         <v>0</v>
       </c>
       <c r="AH16" s="27" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="AI16" s="29" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
@@ -3358,21 +3396,21 @@
       <c r="BE16" s="17"/>
       <c r="BF16" s="17"/>
     </row>
-    <row r="17" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F17" s="5">
         <v>0</v>
@@ -3390,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="L17" s="8">
         <v>0</v>
@@ -3399,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="O17" s="8">
         <v>0</v>
@@ -3408,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="R17" s="8">
         <v>0</v>
@@ -3417,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="U17" s="8">
         <v>0</v>
@@ -3447,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="AE17" s="9">
         <v>0</v>
@@ -3459,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="AH17" s="24" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="AI17" s="26" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="AK17" s="17"/>
       <c r="AL17" s="17"/>
@@ -3487,21 +3525,21 @@
       <c r="BE17" s="17"/>
       <c r="BF17" s="17"/>
     </row>
-    <row r="18" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>5</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>100</v>
+        <v>216</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
@@ -3519,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
@@ -3528,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="O18" s="8">
         <v>0</v>
@@ -3537,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -3546,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="U18" s="8">
         <v>0</v>
@@ -3576,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="8" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="AE18" s="9">
         <v>0</v>
@@ -3588,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AH18" s="27" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="AI18" s="29" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="AK18" s="17"/>
       <c r="AL18" s="17"/>
@@ -3618,25 +3656,25 @@
     </row>
     <row r="19" spans="1:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="F19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H19">
         <v>9</v>
@@ -3648,7 +3686,7 @@
         <v>6</v>
       </c>
       <c r="K19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3657,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O19">
         <v>3</v>
@@ -3666,7 +3704,7 @@
         <v>5</v>
       </c>
       <c r="Q19" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -3675,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U19">
         <v>0</v>
@@ -3708,19 +3746,19 @@
         <v>-2</v>
       </c>
       <c r="AE19" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="AF19" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>118</v>
+        <v>123</v>
+      </c>
+      <c r="AG19">
+        <v>0.5</v>
       </c>
       <c r="AH19" s="24" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AI19" s="26" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="AK19" s="17"/>
       <c r="AL19" s="17"/>
@@ -3751,121 +3789,121 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z18"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>133</v>
+        <v>224</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>134</v>
+        <v>225</v>
       </c>
       <c r="U4" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="V4" t="s">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="W4" t="s">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="X4" t="s">
-        <v>138</v>
+        <v>229</v>
       </c>
       <c r="Y4" t="s">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="Z4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B5">
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -3877,7 +3915,7 @@
         <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -3886,7 +3924,7 @@
         <v>9</v>
       </c>
       <c r="N5" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -3895,22 +3933,22 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R5" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="S5" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="T5" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="U5" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V5" t="s">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="Y5">
         <v>-3.3</v>
@@ -3921,25 +3959,25 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B6">
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="H6">
         <v>11</v>
@@ -3951,7 +3989,7 @@
         <v>9</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -3960,7 +3998,7 @@
         <v>8</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -3969,22 +4007,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R6" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="S6" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="T6" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V6" t="s">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="Y6">
         <v>12.6</v>
@@ -3995,42 +4033,42 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B7">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B8">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -4042,17 +4080,17 @@
         <v>8</v>
       </c>
       <c r="K8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8" t="s">
         <v>61</v>
       </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
-      <c r="N8" t="s">
-        <v>62</v>
-      </c>
       <c r="O8">
         <v>2</v>
       </c>
@@ -4060,22 +4098,22 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="R8" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="S8" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="T8" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="V8" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="Y8">
         <v>2.4</v>
@@ -4086,25 +4124,25 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B9">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="H9">
         <v>19</v>
@@ -4116,7 +4154,7 @@
         <v>12</v>
       </c>
       <c r="K9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L9">
         <v>2</v>
@@ -4125,7 +4163,7 @@
         <v>6</v>
       </c>
       <c r="N9" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -4134,22 +4172,22 @@
         <v>8</v>
       </c>
       <c r="Q9" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="R9" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="S9" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="T9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U9" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="V9" t="s">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="Y9">
         <v>16</v>
@@ -4160,22 +4198,22 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="H10">
         <v>14</v>
@@ -4187,7 +4225,7 @@
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -4196,7 +4234,7 @@
         <v>5</v>
       </c>
       <c r="N10" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -4205,22 +4243,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R10" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="S10" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="T10" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
       <c r="U10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V10" t="s">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="Y10">
         <v>10.8</v>
@@ -4231,25 +4269,25 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B11">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -4261,7 +4299,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -4270,7 +4308,7 @@
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -4279,22 +4317,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R11" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="S11" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="T11" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="U11" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V11" t="s">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="Y11">
         <v>3.2</v>
@@ -4305,25 +4343,25 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -4335,7 +4373,7 @@
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -4344,7 +4382,7 @@
         <v>4</v>
       </c>
       <c r="N12" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -4353,22 +4391,22 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="S12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T12" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="U12" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V12" t="s">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="Y12">
         <v>7.4</v>
@@ -4379,25 +4417,25 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B13">
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -4409,7 +4447,7 @@
         <v>2</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4418,7 +4456,7 @@
         <v>2</v>
       </c>
       <c r="N13" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -4427,22 +4465,22 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R13" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="S13" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="T13" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="U13" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V13" t="s">
-        <v>151</v>
+        <v>242</v>
       </c>
       <c r="Y13">
         <v>-2.6</v>
@@ -4453,42 +4491,42 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B14">
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B15">
         <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -4500,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4509,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -4518,22 +4556,22 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R15" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="S15" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="T15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="Y15">
         <v>-0.4</v>
@@ -4544,25 +4582,25 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B16">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -4574,7 +4612,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4583,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -4592,22 +4630,22 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R16" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="S16" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="T16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="V16" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="Y16">
         <v>3</v>
@@ -4618,36 +4656,36 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>216</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4656,11 +4694,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BA19"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="0" hidden="1"/>
     <col min="34" max="34" width="23.33203125" hidden="1" customWidth="1"/>
     <col min="35" max="35" width="21.109375" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="7.77734375" customWidth="1"/>
@@ -4683,9 +4721,9 @@
     <col min="53" max="53" width="137.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:53" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AH1" s="10"/>
       <c r="AI1" s="10"/>
@@ -4710,7 +4748,7 @@
     </row>
     <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="AH2" s="11"/>
       <c r="AI2" s="11"/>
@@ -4733,9 +4771,9 @@
       <c r="AZ2" s="11"/>
       <c r="BA2" s="11"/>
     </row>
-    <row r="3" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:53" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AK3" s="12" t="s">
-        <v>185</v>
+        <v>2</v>
       </c>
       <c r="AL3" s="12"/>
       <c r="AM3" s="12"/>
@@ -4745,7 +4783,7 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="12" t="s">
-        <v>172</v>
+        <v>3</v>
       </c>
       <c r="AT3" s="12"/>
       <c r="AU3" s="12"/>
@@ -4754,186 +4792,186 @@
       <c r="AX3" s="12"/>
       <c r="AY3" s="13"/>
       <c r="AZ3" s="12" t="s">
-        <v>243</v>
+        <v>4</v>
       </c>
       <c r="BA3" s="12"/>
     </row>
-    <row r="4" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:53" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="U4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="V4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="W4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="X4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AB4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AD4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AE4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AF4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AH4" s="21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AI4" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AJ4" s="23"/>
       <c r="AK4" s="14" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL4" s="14" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="AM4" s="14" t="s">
-        <v>174</v>
+        <v>41</v>
       </c>
       <c r="AN4" s="14" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="AO4" s="14" t="s">
-        <v>176</v>
+        <v>43</v>
       </c>
       <c r="AP4" s="14" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="AQ4" s="14" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="AR4" s="15"/>
       <c r="AS4" s="14" t="s">
-        <v>179</v>
+        <v>46</v>
       </c>
       <c r="AT4" s="14" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="AU4" s="14" t="s">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AV4" s="14" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="AW4" s="14" t="s">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="AX4" s="14" t="s">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="AY4" s="15"/>
       <c r="AZ4" s="14" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="BA4" s="14" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -4945,7 +4983,7 @@
         <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -4954,7 +4992,7 @@
         <v>8</v>
       </c>
       <c r="N5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -4963,7 +5001,7 @@
         <v>5</v>
       </c>
       <c r="Q5" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -4972,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -5005,22 +5043,22 @@
         <v>-8</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="AF5" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="AG5" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="AH5" s="22"/>
       <c r="AI5" s="22"/>
       <c r="AJ5" s="17"/>
       <c r="AK5" s="24" t="s">
-        <v>186</v>
+        <v>66</v>
       </c>
       <c r="AL5" s="25" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="AM5" s="25">
         <v>86.8</v>
@@ -5039,7 +5077,7 @@
       </c>
       <c r="AR5" s="16"/>
       <c r="AS5" s="24" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="AT5" s="30">
         <v>0.52777777777777779</v>
@@ -5058,33 +5096,33 @@
       </c>
       <c r="AY5" s="16"/>
       <c r="AZ5" s="32" t="s">
-        <v>203</v>
+        <v>69</v>
       </c>
       <c r="BA5" s="32" t="s">
-        <v>205</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5096,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -5105,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -5114,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -5123,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -5156,22 +5194,22 @@
         <v>0</v>
       </c>
       <c r="AE6" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AF6" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AG6" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH6" s="22"/>
       <c r="AI6" s="22"/>
       <c r="AJ6" s="17"/>
       <c r="AK6" s="27" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="AL6" s="28" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AM6" s="28">
         <v>90</v>
@@ -5190,7 +5228,7 @@
       </c>
       <c r="AR6" s="16"/>
       <c r="AS6" s="27" t="s">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="AT6" s="31">
         <v>0.30208333333333331</v>
@@ -5209,33 +5247,33 @@
       </c>
       <c r="AY6" s="16"/>
       <c r="AZ6" s="32" t="s">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="BA6" s="32" t="s">
-        <v>206</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -5247,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -5256,7 +5294,7 @@
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -5265,7 +5303,7 @@
         <v>4</v>
       </c>
       <c r="Q7" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -5274,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -5307,22 +5345,22 @@
         <v>-5</v>
       </c>
       <c r="AE7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AF7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="AH7" s="22"/>
       <c r="AI7" s="22"/>
       <c r="AJ7" s="17"/>
       <c r="AK7" s="24" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="AL7" s="25" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="AM7" s="25">
         <v>86.2</v>
@@ -5341,7 +5379,7 @@
       </c>
       <c r="AR7" s="16"/>
       <c r="AS7" s="24" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="AT7" s="30">
         <v>0.28472222222222221</v>
@@ -5360,33 +5398,33 @@
       </c>
       <c r="AY7" s="16"/>
       <c r="AZ7" s="32" t="s">
-        <v>183</v>
+        <v>94</v>
       </c>
       <c r="BA7" s="32" t="s">
-        <v>207</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:53" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -5398,7 +5436,7 @@
         <v>9</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -5407,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -5416,7 +5454,7 @@
         <v>8</v>
       </c>
       <c r="Q8" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -5425,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U8">
         <v>1</v>
@@ -5458,22 +5496,22 @@
         <v>-3</v>
       </c>
       <c r="AE8" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="AF8" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="AG8" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="AH8" s="22"/>
       <c r="AI8" s="22"/>
       <c r="AJ8" s="17"/>
       <c r="AK8" s="27" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AL8" s="28" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AM8" s="28">
         <v>85.8</v>
@@ -5492,7 +5530,7 @@
       </c>
       <c r="AR8" s="16"/>
       <c r="AS8" s="19" t="s">
-        <v>184</v>
+        <v>105</v>
       </c>
       <c r="AT8" s="14"/>
       <c r="AU8" s="20"/>
@@ -5505,25 +5543,25 @@
     </row>
     <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -5535,7 +5573,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L9">
         <v>2</v>
@@ -5544,7 +5582,7 @@
         <v>4</v>
       </c>
       <c r="N9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -5553,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -5562,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U9">
         <v>2</v>
@@ -5595,22 +5633,22 @@
         <v>-2</v>
       </c>
       <c r="AE9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AG9" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH9" s="22"/>
       <c r="AI9" s="22"/>
       <c r="AJ9" s="17"/>
       <c r="AK9" s="24" t="s">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="AL9" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AM9" s="25">
         <v>83.9</v>
@@ -5629,10 +5667,10 @@
       </c>
       <c r="AR9" s="16"/>
       <c r="AS9" s="17" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="AT9" s="25" t="s">
-        <v>197</v>
+        <v>113</v>
       </c>
       <c r="AU9" s="25">
         <v>-4</v>
@@ -5652,25 +5690,25 @@
     </row>
     <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5682,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -5691,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -5700,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -5709,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -5742,22 +5780,22 @@
         <v>0</v>
       </c>
       <c r="AE10" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AF10" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AG10" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH10" s="22"/>
       <c r="AI10" s="22"/>
       <c r="AJ10" s="17"/>
       <c r="AK10" s="27" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="AL10" s="28" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AM10" s="28">
         <v>82.3</v>
@@ -5776,10 +5814,10 @@
       </c>
       <c r="AR10" s="16"/>
       <c r="AS10" s="17" t="s">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="AT10" s="28" t="s">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="AU10" s="28">
         <v>-2</v>
@@ -5799,25 +5837,25 @@
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -5829,7 +5867,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -5838,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O11">
         <v>3</v>
@@ -5847,7 +5885,7 @@
         <v>5</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -5856,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -5889,22 +5927,22 @@
         <v>-2</v>
       </c>
       <c r="AE11" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="AF11" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="AG11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="AH11" s="22"/>
       <c r="AI11" s="22"/>
       <c r="AJ11" s="17"/>
       <c r="AK11" s="24" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="AL11" s="25" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="AM11" s="25">
         <v>82.7</v>
@@ -5923,10 +5961,10 @@
       </c>
       <c r="AR11" s="16"/>
       <c r="AS11" s="17" t="s">
-        <v>202</v>
+        <v>126</v>
       </c>
       <c r="AT11" s="25" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="AU11" s="25">
         <v>-11</v>
@@ -5946,25 +5984,25 @@
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -5976,7 +6014,7 @@
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -5985,7 +6023,7 @@
         <v>6</v>
       </c>
       <c r="N12" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -5994,7 +6032,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -6003,7 +6041,7 @@
         <v>2</v>
       </c>
       <c r="T12" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="U12">
         <v>4</v>
@@ -6036,22 +6074,22 @@
         <v>1</v>
       </c>
       <c r="AE12" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="AF12" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="AG12" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="AH12" s="22"/>
       <c r="AI12" s="22"/>
       <c r="AJ12" s="17"/>
       <c r="AK12" s="27" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="AL12" s="28" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="AM12" s="28">
         <v>77.599999999999994</v>
@@ -6081,25 +6119,25 @@
     </row>
     <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="H13">
         <v>19</v>
@@ -6111,7 +6149,7 @@
         <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L13">
         <v>4</v>
@@ -6120,7 +6158,7 @@
         <v>6</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="O13">
         <v>2</v>
@@ -6129,7 +6167,7 @@
         <v>6</v>
       </c>
       <c r="Q13" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="R13">
         <v>5</v>
@@ -6138,7 +6176,7 @@
         <v>8</v>
       </c>
       <c r="T13" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -6171,22 +6209,22 @@
         <v>-14</v>
       </c>
       <c r="AE13" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="AF13" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="AG13" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH13" s="22"/>
       <c r="AI13" s="22"/>
       <c r="AJ13" s="17"/>
       <c r="AK13" s="24" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="AL13" s="25" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="AM13" s="25">
         <v>77.599999999999994</v>
@@ -6216,25 +6254,25 @@
     </row>
     <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
         <v>121</v>
       </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6246,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -6255,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -6264,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -6273,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -6306,13 +6344,13 @@
         <v>0</v>
       </c>
       <c r="AE14" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AF14" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AG14" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH14" s="22"/>
       <c r="AI14" s="22"/>
@@ -6337,25 +6375,25 @@
     </row>
     <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -6367,7 +6405,7 @@
         <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -6376,7 +6414,7 @@
         <v>2</v>
       </c>
       <c r="N15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O15">
         <v>2</v>
@@ -6385,7 +6423,7 @@
         <v>4</v>
       </c>
       <c r="Q15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -6394,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -6427,13 +6465,13 @@
         <v>-8</v>
       </c>
       <c r="AE15" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AG15" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH15" s="22"/>
       <c r="AI15" s="22"/>
@@ -6458,25 +6496,25 @@
     </row>
     <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="H16">
         <v>6</v>
@@ -6488,7 +6526,7 @@
         <v>21</v>
       </c>
       <c r="K16" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="L16">
         <v>3</v>
@@ -6497,7 +6535,7 @@
         <v>12</v>
       </c>
       <c r="N16" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -6506,7 +6544,7 @@
         <v>9</v>
       </c>
       <c r="Q16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -6515,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -6548,13 +6586,13 @@
         <v>-3</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="AF16" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="AG16" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="AH16" s="22"/>
       <c r="AI16" s="22"/>
@@ -6579,25 +6617,25 @@
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -6609,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -6618,7 +6656,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -6627,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -6636,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -6669,13 +6707,13 @@
         <v>0</v>
       </c>
       <c r="AE17" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AF17" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AG17" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH17" s="22"/>
       <c r="AI17" s="22"/>
@@ -6700,25 +6738,25 @@
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -6730,7 +6768,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -6739,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -6748,7 +6786,7 @@
         <v>2</v>
       </c>
       <c r="Q18" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -6757,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -6790,13 +6828,13 @@
         <v>4</v>
       </c>
       <c r="AE18" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AG18" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AH18" s="22"/>
       <c r="AI18" s="22"/>
@@ -6844,4 +6882,2114 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:BA19"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="33"/>
+      <c r="AN1" s="33"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
+      <c r="AR1" s="33"/>
+      <c r="AS1" s="33"/>
+      <c r="AT1" s="33"/>
+      <c r="AU1" s="33"/>
+      <c r="AV1" s="33"/>
+      <c r="AW1" s="33"/>
+      <c r="AX1" s="33"/>
+      <c r="AY1" s="33"/>
+      <c r="AZ1" s="33"/>
+      <c r="BA1" s="33"/>
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="34"/>
+      <c r="AL2" s="34"/>
+      <c r="AM2" s="34"/>
+      <c r="AN2" s="34"/>
+      <c r="AO2" s="34"/>
+      <c r="AP2" s="34"/>
+      <c r="AQ2" s="34"/>
+      <c r="AR2" s="34"/>
+      <c r="AS2" s="34"/>
+      <c r="AT2" s="34"/>
+      <c r="AU2" s="34"/>
+      <c r="AV2" s="34"/>
+      <c r="AW2" s="34"/>
+      <c r="AX2" s="34"/>
+      <c r="AY2" s="34"/>
+      <c r="AZ2" s="34"/>
+      <c r="BA2" s="34"/>
+    </row>
+    <row r="3" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="AK3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="35"/>
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="35"/>
+      <c r="AP3" s="35"/>
+      <c r="AQ3" s="35"/>
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="35"/>
+      <c r="AU3" s="35"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="36"/>
+      <c r="AZ3" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="BA3" s="35"/>
+    </row>
+    <row r="4" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V4" t="s">
+        <v>26</v>
+      </c>
+      <c r="W4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK4" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL4" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM4" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN4" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO4" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP4" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ4" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR4" s="38"/>
+      <c r="AS4" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT4" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU4" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV4" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW4" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX4" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA4" s="37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+      <c r="N5" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>4</v>
+      </c>
+      <c r="Y5">
+        <v>4</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>2</v>
+      </c>
+      <c r="AB5">
+        <v>4</v>
+      </c>
+      <c r="AC5">
+        <v>14</v>
+      </c>
+      <c r="AD5">
+        <v>-8</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK5" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL5" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM5" s="45">
+        <v>86.8</v>
+      </c>
+      <c r="AN5" s="45">
+        <v>99.6</v>
+      </c>
+      <c r="AO5" s="45">
+        <v>-4</v>
+      </c>
+      <c r="AP5" s="45">
+        <v>-29.7</v>
+      </c>
+      <c r="AQ5" s="46">
+        <v>25.7</v>
+      </c>
+      <c r="AR5" s="39"/>
+      <c r="AS5" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="AT5" s="50">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="AU5" s="45">
+        <v>6</v>
+      </c>
+      <c r="AV5" s="45">
+        <v>108.5</v>
+      </c>
+      <c r="AW5" s="45">
+        <v>94.2</v>
+      </c>
+      <c r="AX5" s="46">
+        <v>14.3</v>
+      </c>
+      <c r="AY5" s="39"/>
+      <c r="AZ5" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA5" s="52" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>63</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6" t="s">
+        <v>63</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK6" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL6" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM6" s="48">
+        <v>90</v>
+      </c>
+      <c r="AN6" s="48">
+        <v>96.4</v>
+      </c>
+      <c r="AO6" s="48">
+        <v>2.4</v>
+      </c>
+      <c r="AP6" s="48">
+        <v>-18.399999999999999</v>
+      </c>
+      <c r="AQ6" s="49">
+        <v>20.8</v>
+      </c>
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT6" s="51">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="AU6" s="48">
+        <v>3</v>
+      </c>
+      <c r="AV6" s="48">
+        <v>98.4</v>
+      </c>
+      <c r="AW6" s="48">
+        <v>88.5</v>
+      </c>
+      <c r="AX6" s="49">
+        <v>9.9</v>
+      </c>
+      <c r="AY6" s="39"/>
+      <c r="AZ6" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="BA6" s="52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>5</v>
+      </c>
+      <c r="W7">
+        <v>5</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
+        <v>3</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7">
+        <v>3</v>
+      </c>
+      <c r="AC7">
+        <v>13</v>
+      </c>
+      <c r="AD7">
+        <v>-5</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK7" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL7" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM7" s="45">
+        <v>86.2</v>
+      </c>
+      <c r="AN7" s="45">
+        <v>100.2</v>
+      </c>
+      <c r="AO7" s="45">
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="AP7" s="45">
+        <v>-15.2</v>
+      </c>
+      <c r="AQ7" s="46">
+        <v>10.1</v>
+      </c>
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT7" s="50">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="AU7" s="45">
+        <v>-7</v>
+      </c>
+      <c r="AV7" s="45">
+        <v>78.5</v>
+      </c>
+      <c r="AW7" s="45">
+        <v>114.2</v>
+      </c>
+      <c r="AX7" s="46">
+        <v>-35.700000000000003</v>
+      </c>
+      <c r="AY7" s="39"/>
+      <c r="AZ7" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA7" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8">
+        <v>11</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>101</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8" t="s">
+        <v>63</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>2</v>
+      </c>
+      <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>3</v>
+      </c>
+      <c r="Y8">
+        <v>4</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>2</v>
+      </c>
+      <c r="AC8">
+        <v>16</v>
+      </c>
+      <c r="AD8">
+        <v>-3</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK8" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL8" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM8" s="48">
+        <v>85.8</v>
+      </c>
+      <c r="AN8" s="48">
+        <v>100.6</v>
+      </c>
+      <c r="AO8" s="48">
+        <v>-6</v>
+      </c>
+      <c r="AP8" s="48">
+        <v>-10.4</v>
+      </c>
+      <c r="AQ8" s="49">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT8" s="37"/>
+      <c r="AU8" s="43"/>
+      <c r="AV8" s="43"/>
+      <c r="AW8" s="43"/>
+      <c r="AX8" s="43"/>
+      <c r="AY8" s="39"/>
+      <c r="AZ8" s="41"/>
+      <c r="BA8" s="41"/>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>4</v>
+      </c>
+      <c r="N9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>63</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>2</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>4</v>
+      </c>
+      <c r="AD9">
+        <v>-2</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK9" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="AL9" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM9" s="45">
+        <v>83.9</v>
+      </c>
+      <c r="AN9" s="45">
+        <v>102.5</v>
+      </c>
+      <c r="AO9" s="45">
+        <v>-9.8000000000000007</v>
+      </c>
+      <c r="AP9" s="45">
+        <v>-7.4</v>
+      </c>
+      <c r="AQ9" s="46">
+        <v>-2.4</v>
+      </c>
+      <c r="AR9" s="39"/>
+      <c r="AS9" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT9" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU9" s="45">
+        <v>-4</v>
+      </c>
+      <c r="AV9" s="45">
+        <v>86.8</v>
+      </c>
+      <c r="AW9" s="45">
+        <v>98.5</v>
+      </c>
+      <c r="AX9" s="46">
+        <v>-11.7</v>
+      </c>
+      <c r="AY9" s="39"/>
+      <c r="AZ9" s="40"/>
+      <c r="BA9" s="40"/>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>63</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10" t="s">
+        <v>63</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK10" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL10" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="AM10" s="48">
+        <v>82.3</v>
+      </c>
+      <c r="AN10" s="48">
+        <v>104.1</v>
+      </c>
+      <c r="AO10" s="48">
+        <v>-13</v>
+      </c>
+      <c r="AP10" s="48">
+        <v>-7.9</v>
+      </c>
+      <c r="AQ10" s="49">
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="AR10" s="39"/>
+      <c r="AS10" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT10" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU10" s="48">
+        <v>-2</v>
+      </c>
+      <c r="AV10" s="48">
+        <v>88.5</v>
+      </c>
+      <c r="AW10" s="48">
+        <v>95.8</v>
+      </c>
+      <c r="AX10" s="49">
+        <v>-7.3</v>
+      </c>
+      <c r="AY10" s="39"/>
+      <c r="AZ10" s="40"/>
+      <c r="BA10" s="40"/>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>122</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>63</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>4</v>
+      </c>
+      <c r="W11">
+        <v>4</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11">
+        <v>3</v>
+      </c>
+      <c r="AC11">
+        <v>10</v>
+      </c>
+      <c r="AD11">
+        <v>-2</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK11" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="AL11" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM11" s="45">
+        <v>82.7</v>
+      </c>
+      <c r="AN11" s="45">
+        <v>103.7</v>
+      </c>
+      <c r="AO11" s="45">
+        <v>-12.3</v>
+      </c>
+      <c r="AP11" s="45">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="46">
+        <v>-12.3</v>
+      </c>
+      <c r="AR11" s="39"/>
+      <c r="AS11" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="AT11" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="AU11" s="45">
+        <v>-11</v>
+      </c>
+      <c r="AV11" s="45">
+        <v>82.4</v>
+      </c>
+      <c r="AW11" s="45">
+        <v>103.5</v>
+      </c>
+      <c r="AX11" s="46">
+        <v>-21.1</v>
+      </c>
+      <c r="AY11" s="39"/>
+      <c r="AZ11" s="40"/>
+      <c r="BA11" s="40"/>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12" t="s">
+        <v>132</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>6</v>
+      </c>
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>61</v>
+      </c>
+      <c r="R12">
+        <v>2</v>
+      </c>
+      <c r="S12">
+        <v>2</v>
+      </c>
+      <c r="T12" t="s">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>4</v>
+      </c>
+      <c r="V12">
+        <v>5</v>
+      </c>
+      <c r="W12">
+        <v>9</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>2</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>6</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK12" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="AL12" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM12" s="48">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="AN12" s="48">
+        <v>108.8</v>
+      </c>
+      <c r="AO12" s="48">
+        <v>-22.4</v>
+      </c>
+      <c r="AP12" s="48">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="49">
+        <v>-22.4</v>
+      </c>
+      <c r="AR12" s="39"/>
+      <c r="AS12" s="40"/>
+      <c r="AT12" s="40"/>
+      <c r="AU12" s="40"/>
+      <c r="AV12" s="40"/>
+      <c r="AW12" s="40"/>
+      <c r="AX12" s="40"/>
+      <c r="AY12" s="39"/>
+      <c r="AZ12" s="40"/>
+      <c r="BA12" s="40"/>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13">
+        <v>19</v>
+      </c>
+      <c r="I13">
+        <v>6</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>6</v>
+      </c>
+      <c r="N13" t="s">
+        <v>141</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>87</v>
+      </c>
+      <c r="R13">
+        <v>5</v>
+      </c>
+      <c r="S13">
+        <v>8</v>
+      </c>
+      <c r="T13" t="s">
+        <v>142</v>
+      </c>
+      <c r="U13">
+        <v>5</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>15</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>2</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>3</v>
+      </c>
+      <c r="AB13">
+        <v>5</v>
+      </c>
+      <c r="AC13">
+        <v>25</v>
+      </c>
+      <c r="AD13">
+        <v>-14</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>143</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK13" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="AL13" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="AM13" s="45">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="AN13" s="45">
+        <v>108.8</v>
+      </c>
+      <c r="AO13" s="45">
+        <v>-22.5</v>
+      </c>
+      <c r="AP13" s="45">
+        <v>20.7</v>
+      </c>
+      <c r="AQ13" s="46">
+        <v>-43.2</v>
+      </c>
+      <c r="AR13" s="39"/>
+      <c r="AS13" s="40"/>
+      <c r="AT13" s="40"/>
+      <c r="AU13" s="40"/>
+      <c r="AV13" s="40"/>
+      <c r="AW13" s="40"/>
+      <c r="AX13" s="40"/>
+      <c r="AY13" s="39"/>
+      <c r="AZ13" s="40"/>
+      <c r="BA13" s="40"/>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>63</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>63</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
+        <v>63</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="40"/>
+      <c r="AM14" s="40"/>
+      <c r="AN14" s="40"/>
+      <c r="AO14" s="40"/>
+      <c r="AP14" s="40"/>
+      <c r="AQ14" s="40"/>
+      <c r="AR14" s="39"/>
+      <c r="AS14" s="40"/>
+      <c r="AT14" s="40"/>
+      <c r="AU14" s="40"/>
+      <c r="AV14" s="40"/>
+      <c r="AW14" s="40"/>
+      <c r="AX14" s="40"/>
+      <c r="AY14" s="39"/>
+      <c r="AZ14" s="40"/>
+      <c r="BA14" s="40"/>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15" t="s">
+        <v>63</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15" t="s">
+        <v>63</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15">
+        <v>2</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>4</v>
+      </c>
+      <c r="AD15">
+        <v>-8</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="40"/>
+      <c r="AN15" s="40"/>
+      <c r="AO15" s="40"/>
+      <c r="AP15" s="40"/>
+      <c r="AQ15" s="40"/>
+      <c r="AR15" s="39"/>
+      <c r="AS15" s="40"/>
+      <c r="AT15" s="40"/>
+      <c r="AU15" s="40"/>
+      <c r="AV15" s="40"/>
+      <c r="AW15" s="40"/>
+      <c r="AX15" s="40"/>
+      <c r="AY15" s="39"/>
+      <c r="AZ15" s="40"/>
+      <c r="BA15" s="40"/>
+    </row>
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>154</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <v>12</v>
+      </c>
+      <c r="N16" t="s">
+        <v>88</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>9</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>63</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
+        <v>63</v>
+      </c>
+      <c r="U16">
+        <v>4</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16">
+        <v>6</v>
+      </c>
+      <c r="X16">
+        <v>3</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>3</v>
+      </c>
+      <c r="AA16">
+        <v>3</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+      <c r="AC16">
+        <v>-3</v>
+      </c>
+      <c r="AD16">
+        <v>-3</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="40"/>
+      <c r="AN16" s="40"/>
+      <c r="AO16" s="40"/>
+      <c r="AP16" s="40"/>
+      <c r="AQ16" s="40"/>
+      <c r="AR16" s="39"/>
+      <c r="AS16" s="40"/>
+      <c r="AT16" s="40"/>
+      <c r="AU16" s="40"/>
+      <c r="AV16" s="40"/>
+      <c r="AW16" s="40"/>
+      <c r="AX16" s="40"/>
+      <c r="AY16" s="39"/>
+      <c r="AZ16" s="40"/>
+      <c r="BA16" s="40"/>
+    </row>
+    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>63</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17" t="s">
+        <v>63</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK17" s="40"/>
+      <c r="AL17" s="40"/>
+      <c r="AM17" s="40"/>
+      <c r="AN17" s="40"/>
+      <c r="AO17" s="40"/>
+      <c r="AP17" s="40"/>
+      <c r="AQ17" s="40"/>
+      <c r="AR17" s="39"/>
+      <c r="AS17" s="40"/>
+      <c r="AT17" s="40"/>
+      <c r="AU17" s="40"/>
+      <c r="AV17" s="40"/>
+      <c r="AW17" s="40"/>
+      <c r="AX17" s="40"/>
+      <c r="AY17" s="39"/>
+      <c r="AZ17" s="40"/>
+      <c r="BA17" s="40"/>
+    </row>
+    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>164</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>63</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>63</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18" t="s">
+        <v>63</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>3</v>
+      </c>
+      <c r="AC18">
+        <v>-2</v>
+      </c>
+      <c r="AD18">
+        <v>4</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK18" s="40"/>
+      <c r="AL18" s="40"/>
+      <c r="AM18" s="40"/>
+      <c r="AN18" s="40"/>
+      <c r="AO18" s="40"/>
+      <c r="AP18" s="40"/>
+      <c r="AQ18" s="40"/>
+      <c r="AR18" s="39"/>
+      <c r="AS18" s="40"/>
+      <c r="AT18" s="40"/>
+      <c r="AU18" s="40"/>
+      <c r="AV18" s="40"/>
+      <c r="AW18" s="40"/>
+      <c r="AX18" s="40"/>
+      <c r="AY18" s="39"/>
+      <c r="AZ18" s="40"/>
+      <c r="BA18" s="40"/>
+    </row>
+    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="AK19" s="40"/>
+      <c r="AL19" s="40"/>
+      <c r="AM19" s="40"/>
+      <c r="AN19" s="40"/>
+      <c r="AO19" s="40"/>
+      <c r="AP19" s="40"/>
+      <c r="AQ19" s="40"/>
+      <c r="AR19" s="40"/>
+      <c r="AS19" s="40"/>
+      <c r="AT19" s="40"/>
+      <c r="AU19" s="40"/>
+      <c r="AV19" s="40"/>
+      <c r="AW19" s="40"/>
+      <c r="AX19" s="40"/>
+      <c r="AY19" s="40"/>
+      <c r="AZ19" s="40"/>
+      <c r="BA19" s="40"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>